--- a/reports/Vulnerability_Test_Report.xlsx
+++ b/reports/Vulnerability_Test_Report.xlsx
@@ -1355,7 +1355,7 @@
         <v>Audit Date:</v>
       </c>
       <c r="B3" s="5" t="str">
-        <v>26/10/2026, 17:12:24</v>
+        <v>26/10/2026, 17:13:26</v>
       </c>
       <c r="D3" s="6" t="str">
         <v>Overall Security Status:</v>
@@ -12855,7 +12855,7 @@
         <v>Git ref</v>
       </c>
       <c r="B6" s="24" t="str">
-        <v>local</v>
+        <v>arena/b28508eb-abet</v>
       </c>
     </row>
     <row r="7">
@@ -12863,7 +12863,7 @@
         <v>Commit SHA</v>
       </c>
       <c r="B7" s="26" t="str">
-        <v>local</v>
+        <v>a9ce338dbdf85acc3bff13761404a7384b4ca9c2</v>
       </c>
     </row>
     <row r="8">
@@ -12871,7 +12871,7 @@
         <v>Workflow run id</v>
       </c>
       <c r="B8" s="24" t="str">
-        <v>local</v>
+        <v>40366447539</v>
       </c>
     </row>
     <row r="9">
@@ -12879,7 +12879,7 @@
         <v>CI runner</v>
       </c>
       <c r="B9" s="26" t="str">
-        <v>local</v>
+        <v>Linux-X64</v>
       </c>
     </row>
     <row r="10">
@@ -12887,7 +12887,7 @@
         <v>Node.js</v>
       </c>
       <c r="B10" s="24" t="str">
-        <v>v22.22.3</v>
+        <v>v22.23.3</v>
       </c>
     </row>
     <row r="11">
@@ -12935,7 +12935,7 @@
         <v>Started at (UTC)</v>
       </c>
       <c r="B16" s="24" t="str">
-        <v>2026-10-26T17:12:23.725Z</v>
+        <v>2026-10-26T17:13:26.624Z</v>
       </c>
     </row>
     <row r="17">
@@ -12943,7 +12943,7 @@
         <v>Finished at (UTC)</v>
       </c>
       <c r="B17" s="26" t="str">
-        <v>2026-10-26T17:12:24.058Z</v>
+        <v>2026-10-26T17:13:26.985Z</v>
       </c>
     </row>
     <row r="18">
@@ -12951,7 +12951,7 @@
         <v>Duration (s)</v>
       </c>
       <c r="B18" s="24">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Vulnerability_Test_Report.xlsx
+++ b/reports/Vulnerability_Test_Report.xlsx
@@ -1295,7 +1295,7 @@
         <v>Audit Date:</v>
       </c>
       <c r="B3" s="5" t="str">
-        <v>26/10/2026, 17:34:03</v>
+        <v>26/10/2026, 17:35:05</v>
       </c>
       <c r="D3" s="6" t="str">
         <v>Overall Security Status:</v>
@@ -12261,7 +12261,7 @@
         <v>Git ref</v>
       </c>
       <c r="B6" s="24" t="str">
-        <v>local</v>
+        <v>arena/b28508eb-abet</v>
       </c>
     </row>
     <row r="7">
@@ -12269,7 +12269,7 @@
         <v>Commit SHA</v>
       </c>
       <c r="B7" s="25" t="str">
-        <v>local</v>
+        <v>0cee3c6ca348c3ff59a063340774eb0d9782a291</v>
       </c>
     </row>
     <row r="8">
@@ -12277,7 +12277,7 @@
         <v>Workflow run id</v>
       </c>
       <c r="B8" s="24" t="str">
-        <v>local</v>
+        <v>40369854617</v>
       </c>
     </row>
     <row r="9">
@@ -12285,7 +12285,7 @@
         <v>CI runner</v>
       </c>
       <c r="B9" s="25" t="str">
-        <v>local</v>
+        <v>Linux-X64</v>
       </c>
     </row>
     <row r="10">
@@ -12293,7 +12293,7 @@
         <v>Node.js</v>
       </c>
       <c r="B10" s="24" t="str">
-        <v>v22.22.3</v>
+        <v>v22.23.3</v>
       </c>
     </row>
     <row r="11">
@@ -12341,7 +12341,7 @@
         <v>Started at (UTC)</v>
       </c>
       <c r="B16" s="24" t="str">
-        <v>2026-10-26T17:34:02.439Z</v>
+        <v>2026-10-26T17:35:04.994Z</v>
       </c>
     </row>
     <row r="17">
@@ -12349,7 +12349,7 @@
         <v>Finished at (UTC)</v>
       </c>
       <c r="B17" s="25" t="str">
-        <v>2026-10-26T17:34:03.202Z</v>
+        <v>2026-10-26T17:35:05.795Z</v>
       </c>
     </row>
     <row r="18">
@@ -12357,7 +12357,7 @@
         <v>Duration (s)</v>
       </c>
       <c r="B18" s="24">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
